--- a/tools/importer/reports/import-home.report.xlsx
+++ b/tools/importer/reports/import-home.report.xlsx
@@ -52,7 +52,7 @@
     <t>home</t>
   </si>
   <si>
-    <t>2026-10-15T10:05:27.121Z</t>
+    <t>2026-10-15T12:54:44.511Z</t>
   </si>
   <si>
     <t>Servier - Laboratoire pharmaceutique international indépendant</t>
